--- a/COMP.xlsx
+++ b/COMP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\COMPARTIDO\COMPARADOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274214C9-2FE1-4E9D-BF68-05B1FD0C6D15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A95CAB5-E0A9-4899-89F8-B22306F0B9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{8A7EED44-085A-4DEB-BD58-A043D06AE3A9}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="882">
   <si>
     <t>EQUIPO</t>
   </si>
@@ -1730,9 +1730,6 @@
     <t>210 g</t>
   </si>
   <si>
-    <t>IP 68</t>
-  </si>
-  <si>
     <t>144 Hz</t>
   </si>
   <si>
@@ -2636,9 +2633,6 @@
     <t>FACEID</t>
   </si>
   <si>
-    <t>7 años desde 2026</t>
-  </si>
-  <si>
     <t>32 Mpx	(ƒ/ 2.0) + AUX (POSIBLE)</t>
   </si>
   <si>
@@ -2715,6 +2709,54 @@
   </si>
   <si>
     <t>Snapdragon 8 Elite Gen 5 (3 nm)</t>
+  </si>
+  <si>
+    <t>Hasta Agosto 2028</t>
+  </si>
+  <si>
+    <t>Hasta Febrero 2033</t>
+  </si>
+  <si>
+    <t>Hasta Agosto 2031</t>
+  </si>
+  <si>
+    <t>Hasta Septiembre 2031</t>
+  </si>
+  <si>
+    <t>Hasta Noviembre 2030</t>
+  </si>
+  <si>
+    <t>Hasta Marzo 2031</t>
+  </si>
+  <si>
+    <t>Hasta Marzo 2032</t>
+  </si>
+  <si>
+    <t>Hasta Enero 2031</t>
+  </si>
+  <si>
+    <t>Hasta Mayo 2031</t>
+  </si>
+  <si>
+    <t>Hasta Enero 2029</t>
+  </si>
+  <si>
+    <t>8 GB (física) + hasta 16 GB (RAM Boost)</t>
+  </si>
+  <si>
+    <t>Hasta el 2031</t>
+  </si>
+  <si>
+    <t>Hasta el 2029</t>
+  </si>
+  <si>
+    <t>Hasta Febrero 2028</t>
+  </si>
+  <si>
+    <t>Hasta el 2028</t>
+  </si>
+  <si>
+    <t>Hasta el 2030</t>
   </si>
 </sst>
 </file>
@@ -3541,7 +3583,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="B6" s="15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>28</v>
@@ -4321,7 +4363,7 @@
         <v>155</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>194</v>
@@ -4415,7 +4457,7 @@
     </row>
     <row r="3" spans="1:32">
       <c r="A3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B3" s="1">
         <f>IFERROR(
@@ -4430,10 +4472,10 @@
         <v>58</v>
       </c>
       <c r="D3" t="s">
+        <v>698</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>699</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>700</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>19</v>
@@ -4442,10 +4484,10 @@
         <v>169</v>
       </c>
       <c r="H3" t="s">
+        <v>700</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>701</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>702</v>
       </c>
       <c r="J3" t="s">
         <v>463</v>
@@ -4457,7 +4499,7 @@
         <v>468</v>
       </c>
       <c r="M3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>20</v>
@@ -4469,10 +4511,10 @@
         <v>182</v>
       </c>
       <c r="Q3" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>704</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>705</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>20</v>
@@ -4652,7 +4694,7 @@
     </row>
     <row r="6" spans="1:32">
       <c r="A6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B6" s="1">
         <f>IFERROR(
@@ -4667,10 +4709,10 @@
         <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F6" t="s">
         <v>166</v>
@@ -4682,7 +4724,7 @@
         <v>192</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J6" t="s">
         <v>464</v>
@@ -4694,7 +4736,7 @@
         <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>20</v>
@@ -4706,7 +4748,7 @@
         <v>183</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="R6" s="1" t="s">
         <v>189</v>
@@ -4880,8 +4922,8 @@
       <c r="V8" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W8" s="33">
-        <v>47849</v>
+      <c r="W8" s="33" t="s">
+        <v>873</v>
       </c>
       <c r="AF8">
         <v>69.900000000000006</v>
@@ -4889,7 +4931,7 @@
     </row>
     <row r="9" spans="1:32">
       <c r="A9" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B9" s="1">
         <f>IFERROR(
@@ -4904,22 +4946,22 @@
         <v>240</v>
       </c>
       <c r="D9" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>532</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>168</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="J9" t="s">
         <v>464</v>
@@ -4943,7 +4985,7 @@
         <v>181</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="R9" s="1" t="s">
         <v>186</v>
@@ -4966,7 +5008,7 @@
     </row>
     <row r="10" spans="1:32">
       <c r="A10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B10" s="1">
         <f>IFERROR(
@@ -4981,22 +5023,22 @@
         <v>157</v>
       </c>
       <c r="D10" t="s">
+        <v>563</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="22" t="s">
         <v>565</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>566</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>168</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="J10" t="s">
         <v>464</v>
@@ -5020,10 +5062,10 @@
         <v>181</v>
       </c>
       <c r="Q10" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>569</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>20</v>
@@ -5114,8 +5156,8 @@
       <c r="V11" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W11" s="33">
-        <v>47969</v>
+      <c r="W11" s="33" t="s">
+        <v>874</v>
       </c>
       <c r="AF11">
         <v>79.900000000000006</v>
@@ -5156,10 +5198,10 @@
         <v>500</v>
       </c>
       <c r="J12" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="K12" t="s">
-        <v>171</v>
+        <v>594</v>
       </c>
       <c r="L12" t="s">
         <v>20</v>
@@ -5194,8 +5236,8 @@
       <c r="V12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W12" s="33">
-        <v>46753</v>
+      <c r="W12" s="33" t="s">
+        <v>880</v>
       </c>
       <c r="AF12">
         <v>99.9</v>
@@ -5218,10 +5260,10 @@
         <v>355</v>
       </c>
       <c r="D13" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F13" t="s">
         <v>202</v>
@@ -5230,22 +5272,22 @@
         <v>204</v>
       </c>
       <c r="H13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J13" t="s">
+        <v>593</v>
+      </c>
+      <c r="K13" t="s">
         <v>594</v>
-      </c>
-      <c r="K13" t="s">
-        <v>595</v>
       </c>
       <c r="L13" t="s">
         <v>20</v>
       </c>
       <c r="M13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>174</v>
@@ -5257,7 +5299,7 @@
         <v>206</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="R13" s="1" t="s">
         <v>222</v>
@@ -5274,8 +5316,8 @@
       <c r="V13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W13" s="20" t="s">
-        <v>19</v>
+      <c r="W13" s="33" t="s">
+        <v>878</v>
       </c>
     </row>
     <row r="14" spans="1:32">
@@ -5295,10 +5337,10 @@
         <v>416</v>
       </c>
       <c r="D14" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F14" t="s">
         <v>202</v>
@@ -5307,22 +5349,22 @@
         <v>204</v>
       </c>
       <c r="H14" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="J14" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="K14" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="L14" t="s">
         <v>20</v>
       </c>
       <c r="M14" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>174</v>
@@ -5334,7 +5376,7 @@
         <v>206</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="R14" s="1" t="s">
         <v>222</v>
@@ -5351,13 +5393,13 @@
       <c r="V14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W14" s="20" t="s">
-        <v>19</v>
+      <c r="W14" s="33" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="15" spans="1:32">
       <c r="A15" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B15" s="1">
         <f>IFERROR(
@@ -5372,10 +5414,10 @@
         <v>507</v>
       </c>
       <c r="D15" t="s">
+        <v>600</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>601</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>602</v>
       </c>
       <c r="F15" t="s">
         <v>202</v>
@@ -5384,34 +5426,34 @@
         <v>168</v>
       </c>
       <c r="H15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="J15" t="s">
+        <v>599</v>
+      </c>
+      <c r="K15" t="s">
         <v>606</v>
-      </c>
-      <c r="J15" t="s">
-        <v>600</v>
-      </c>
-      <c r="K15" t="s">
-        <v>607</v>
       </c>
       <c r="L15" t="s">
         <v>20</v>
       </c>
       <c r="M15" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="N15" s="1" t="s">
         <v>174</v>
       </c>
       <c r="O15" t="s">
+        <v>607</v>
+      </c>
+      <c r="P15" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="Q15" s="1" t="s">
         <v>609</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>610</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>222</v>
@@ -5428,13 +5470,13 @@
       <c r="V15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="W15" s="20" t="s">
-        <v>19</v>
+      <c r="W15" s="33" t="s">
+        <v>877</v>
       </c>
     </row>
     <row r="16" spans="1:32">
       <c r="A16" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B16" s="1">
         <f>IFERROR(
@@ -5449,10 +5491,10 @@
         <v>870</v>
       </c>
       <c r="D16" t="s">
+        <v>829</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>830</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>831</v>
       </c>
       <c r="F16" t="s">
         <v>202</v>
@@ -5461,40 +5503,40 @@
         <v>168</v>
       </c>
       <c r="H16" t="s">
+        <v>831</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" t="s">
         <v>833</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>834</v>
-      </c>
-      <c r="K16" t="s">
-        <v>835</v>
       </c>
       <c r="L16" t="s">
         <v>20</v>
       </c>
       <c r="M16" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="N16" s="1" t="s">
         <v>174</v>
       </c>
       <c r="O16" t="s">
+        <v>607</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="P16" s="1" t="s">
-        <v>609</v>
-      </c>
       <c r="Q16" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="R16" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>838</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>839</v>
       </c>
       <c r="T16" s="1">
         <v>6</v>
@@ -5503,10 +5545,10 @@
         <v>174</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>840</v>
-      </c>
-      <c r="W16" s="20" t="s">
-        <v>841</v>
+        <v>839</v>
+      </c>
+      <c r="W16" s="33" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="17" spans="1:32">
@@ -5582,8 +5624,8 @@
       <c r="V17" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="W17" s="20">
-        <v>46784</v>
+      <c r="W17" s="33" t="s">
+        <v>879</v>
       </c>
       <c r="AF17" t="s">
         <v>454</v>
@@ -5591,7 +5633,7 @@
     </row>
     <row r="18" spans="1:32">
       <c r="A18" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B18" s="1">
         <f>IFERROR(
@@ -5633,7 +5675,7 @@
         <v>468</v>
       </c>
       <c r="M18" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>20</v>
@@ -5663,7 +5705,7 @@
         <v>195</v>
       </c>
       <c r="W18" s="20" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="19" spans="1:32">
@@ -5745,7 +5787,7 @@
     </row>
     <row r="20" spans="1:32">
       <c r="A20" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B20" s="1">
         <f>IFERROR(
@@ -5787,7 +5829,7 @@
         <v>19</v>
       </c>
       <c r="M20" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="N20" s="1" t="s">
         <v>20</v>
@@ -5899,7 +5941,7 @@
     </row>
     <row r="22" spans="1:32">
       <c r="A22" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B22" s="1">
         <f>IFERROR(
@@ -5914,22 +5956,22 @@
         <v>134</v>
       </c>
       <c r="D22" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="F22" s="22" t="s">
         <v>712</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>713</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>168</v>
       </c>
       <c r="H22" s="22" t="s">
+        <v>713</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>715</v>
       </c>
       <c r="J22" t="s">
         <v>469</v>
@@ -5941,7 +5983,7 @@
         <v>467</v>
       </c>
       <c r="M22" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="N22" s="1" t="s">
         <v>174</v>
@@ -6047,13 +6089,13 @@
       <c r="V23" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W23" s="18" t="s">
-        <v>479</v>
+      <c r="W23" t="s">
+        <v>878</v>
       </c>
     </row>
     <row r="24" spans="1:32">
       <c r="A24" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B24" s="1">
         <f>IFERROR(
@@ -6071,22 +6113,22 @@
         <v>536</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F24" t="s">
         <v>210</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J24" t="s">
-        <v>464</v>
+        <v>876</v>
       </c>
       <c r="K24" t="s">
         <v>233</v>
@@ -6095,7 +6137,7 @@
         <v>20</v>
       </c>
       <c r="M24" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>174</v>
@@ -6119,13 +6161,13 @@
         <v>6</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>174</v>
+        <v>851</v>
       </c>
       <c r="V24" s="1" t="s">
         <v>144</v>
       </c>
       <c r="W24" s="18" t="s">
-        <v>481</v>
+        <v>877</v>
       </c>
     </row>
     <row r="25" spans="1:32">
@@ -6361,7 +6403,7 @@
     </row>
     <row r="28" spans="1:32">
       <c r="A28" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B28" s="1">
         <f>IFERROR(
@@ -6376,13 +6418,13 @@
         <v>113</v>
       </c>
       <c r="D28" t="s">
+        <v>652</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>654</v>
-      </c>
       <c r="F28" s="22" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>102</v>
@@ -6415,7 +6457,7 @@
         <v>182</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>238</v>
@@ -6438,7 +6480,7 @@
     </row>
     <row r="29" spans="1:32">
       <c r="A29" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B29" s="1">
         <f>IFERROR(
@@ -6459,7 +6501,7 @@
         <v>277</v>
       </c>
       <c r="F29" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>102</v>
@@ -6468,7 +6510,7 @@
         <v>230</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J29" t="s">
         <v>464</v>
@@ -6492,10 +6534,10 @@
         <v>181</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>20</v>
@@ -6660,8 +6702,8 @@
       <c r="V31" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="W31" s="33">
-        <v>46966</v>
+      <c r="W31" s="33" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="32" spans="1:32">
@@ -6737,13 +6779,13 @@
       <c r="V32" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="W32" s="33">
-        <v>48061</v>
+      <c r="W32" s="33" t="s">
+        <v>868</v>
       </c>
     </row>
     <row r="33" spans="1:23">
       <c r="A33" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B33" s="1">
         <f>IFERROR(
@@ -6770,10 +6812,10 @@
         <v>169</v>
       </c>
       <c r="H33" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J33" t="s">
         <v>473</v>
@@ -6814,8 +6856,8 @@
       <c r="V33" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="W33" s="33">
-        <v>48092</v>
+      <c r="W33" s="33" t="s">
+        <v>869</v>
       </c>
     </row>
     <row r="34" spans="1:23">
@@ -6891,8 +6933,8 @@
       <c r="V34" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="W34" s="33">
-        <v>47788</v>
+      <c r="W34" s="33" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="35" spans="1:23">
@@ -6968,8 +7010,8 @@
       <c r="V35" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="W35" s="33">
-        <v>47908</v>
+      <c r="W35" s="33" t="s">
+        <v>871</v>
       </c>
     </row>
     <row r="36" spans="1:23">
@@ -7045,13 +7087,13 @@
       <c r="V36" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W36" s="33">
-        <v>47908</v>
+      <c r="W36" s="33" t="s">
+        <v>871</v>
       </c>
     </row>
     <row r="37" spans="1:23">
       <c r="A37" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B37" s="1">
         <f>IFERROR(
@@ -7078,10 +7120,10 @@
         <v>168</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="J37" t="s">
         <v>473</v>
@@ -7093,7 +7135,7 @@
         <v>19</v>
       </c>
       <c r="M37" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>174</v>
@@ -7122,8 +7164,8 @@
       <c r="V37" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W37" s="33">
-        <v>48274</v>
+      <c r="W37" s="33" t="s">
+        <v>872</v>
       </c>
     </row>
     <row r="38" spans="1:23">
@@ -7199,13 +7241,13 @@
       <c r="V38" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W38" s="33">
-        <v>48274</v>
+      <c r="W38" s="33" t="s">
+        <v>872</v>
       </c>
     </row>
     <row r="39" spans="1:23">
       <c r="A39" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B39" s="1">
         <f>IFERROR(
@@ -7220,7 +7262,7 @@
         <v>275</v>
       </c>
       <c r="D39" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F39" s="22" t="s">
         <v>202</v>
@@ -7229,10 +7271,10 @@
         <v>168</v>
       </c>
       <c r="H39" s="22" t="s">
+        <v>739</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>740</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>741</v>
       </c>
       <c r="J39" t="s">
         <v>473</v>
@@ -7244,7 +7286,7 @@
         <v>19</v>
       </c>
       <c r="M39" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>174</v>
@@ -7273,13 +7315,13 @@
       <c r="V39" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W39" s="33">
-        <v>48274</v>
+      <c r="W39" s="33" t="s">
+        <v>872</v>
       </c>
     </row>
     <row r="40" spans="1:23">
       <c r="A40" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B40" s="1">
         <f>IFERROR(
@@ -7294,10 +7336,10 @@
         <v>538</v>
       </c>
       <c r="D40" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="F40" s="22" t="s">
         <v>202</v>
@@ -7306,40 +7348,40 @@
         <v>168</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="I40" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="J40" t="s">
+        <v>847</v>
+      </c>
+      <c r="K40" t="s">
         <v>848</v>
-      </c>
-      <c r="J40" t="s">
-        <v>849</v>
-      </c>
-      <c r="K40" t="s">
-        <v>850</v>
       </c>
       <c r="L40" t="s">
         <v>20</v>
       </c>
       <c r="M40" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>174</v>
       </c>
       <c r="O40" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>269</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>256</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="T40" s="19">
         <v>5.4</v>
@@ -7350,13 +7392,13 @@
       <c r="V40" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W40" s="33">
-        <v>48611</v>
+      <c r="W40" s="33" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="41" spans="1:23">
       <c r="A41" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B41" s="1">
         <f>IFERROR(
@@ -7371,7 +7413,7 @@
         <v>646</v>
       </c>
       <c r="D41" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>211</v>
@@ -7383,40 +7425,40 @@
         <v>168</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="I41" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="J41" t="s">
+        <v>847</v>
+      </c>
+      <c r="K41" t="s">
         <v>848</v>
-      </c>
-      <c r="J41" t="s">
-        <v>849</v>
-      </c>
-      <c r="K41" t="s">
-        <v>850</v>
       </c>
       <c r="L41" t="s">
         <v>20</v>
       </c>
       <c r="M41" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>174</v>
       </c>
       <c r="O41" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>269</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="R41" s="1" t="s">
         <v>257</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="T41" s="19">
         <v>5.4</v>
@@ -7427,13 +7469,13 @@
       <c r="V41" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W41" s="33">
-        <v>48611</v>
+      <c r="W41" s="33" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="42" spans="1:23">
       <c r="A42" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B42" s="1">
         <f>IFERROR(
@@ -7448,10 +7490,10 @@
         <v>754</v>
       </c>
       <c r="D42" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F42" s="22" t="s">
         <v>202</v>
@@ -7460,25 +7502,25 @@
         <v>168</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="J42" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="K42" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="M42" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>174</v>
       </c>
       <c r="O42" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>269</v>
@@ -7487,10 +7529,10 @@
         <v>201</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="T42" s="19">
         <v>6</v>
@@ -7501,8 +7543,8 @@
       <c r="V42" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W42" s="33">
-        <v>48611</v>
+      <c r="W42" s="33" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="43" spans="1:23">
@@ -7534,7 +7576,7 @@
         <v>168</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>533</v>
@@ -7584,7 +7626,7 @@
     </row>
     <row r="44" spans="1:23">
       <c r="A44" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B44" s="1">
         <f>IFERROR(
@@ -7602,7 +7644,7 @@
         <v>531</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F44" t="s">
         <v>17</v>
@@ -7611,7 +7653,7 @@
         <v>168</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>533</v>
@@ -7626,7 +7668,7 @@
         <v>174</v>
       </c>
       <c r="M44" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>20</v>
@@ -7732,13 +7774,13 @@
       <c r="V45" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="W45" s="33">
-        <v>48061</v>
+      <c r="W45" s="33" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="46" spans="1:23">
       <c r="A46" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B46" s="1">
         <f>IFERROR(
@@ -7753,22 +7795,22 @@
         <v>74</v>
       </c>
       <c r="D46" t="s">
+        <v>625</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>627</v>
       </c>
       <c r="F46" t="s">
         <v>21</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H46" t="s">
+        <v>627</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>628</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>629</v>
       </c>
       <c r="J46" t="s">
         <v>464</v>
@@ -7780,7 +7822,7 @@
         <v>467</v>
       </c>
       <c r="M46" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>20</v>
@@ -7792,7 +7834,7 @@
         <v>183</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>273</v>
@@ -7815,7 +7857,7 @@
     </row>
     <row r="47" spans="1:23">
       <c r="A47" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B47" s="1">
         <f>IFERROR(
@@ -7857,7 +7899,7 @@
         <v>470</v>
       </c>
       <c r="M47" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="N47" s="1" t="s">
         <v>20</v>
@@ -7892,7 +7934,7 @@
     </row>
     <row r="48" spans="1:23">
       <c r="A48" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B48" s="1">
         <f>IFERROR(
@@ -7907,34 +7949,34 @@
         <v>185</v>
       </c>
       <c r="D48" t="s">
+        <v>667</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="F48" s="22" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>168</v>
       </c>
       <c r="H48" s="22" t="s">
+        <v>719</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>721</v>
       </c>
       <c r="J48" t="s">
         <v>464</v>
       </c>
       <c r="K48" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="L48" t="s">
         <v>20</v>
       </c>
       <c r="M48" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>174</v>
@@ -7946,7 +7988,7 @@
         <v>270</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="R48" s="1" t="s">
         <v>257</v>
@@ -7969,7 +8011,7 @@
     </row>
     <row r="49" spans="1:23">
       <c r="A49" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B49" s="1">
         <f>IFERROR(
@@ -7984,34 +8026,34 @@
         <v>258</v>
       </c>
       <c r="D49" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>168</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="J49" t="s">
         <v>465</v>
       </c>
       <c r="K49" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="L49" t="s">
         <v>20</v>
       </c>
       <c r="M49" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="N49" s="1" t="s">
         <v>174</v>
@@ -8023,10 +8065,10 @@
         <v>221</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="S49" s="1" t="s">
         <v>20</v>
@@ -8117,8 +8159,8 @@
       <c r="V50" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W50" s="33">
-        <v>47908</v>
+      <c r="W50" s="33" t="s">
+        <v>871</v>
       </c>
     </row>
     <row r="51" spans="1:23">
@@ -8194,8 +8236,8 @@
       <c r="V51" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="W51" s="33">
-        <v>47119</v>
+      <c r="W51" s="33" t="s">
+        <v>875</v>
       </c>
     </row>
     <row r="52" spans="1:23">
@@ -8221,16 +8263,16 @@
         <v>538</v>
       </c>
       <c r="F52" s="22" t="s">
-        <v>539</v>
+        <v>202</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>168</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J52" t="s">
         <v>464</v>
@@ -8254,10 +8296,10 @@
         <v>270</v>
       </c>
       <c r="Q52" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="R52" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="R52" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="S52" s="1" t="s">
         <v>20</v>
@@ -8298,28 +8340,28 @@
         <v>538</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>539</v>
+        <v>202</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>168</v>
       </c>
       <c r="H53" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="J53" t="s">
         <v>465</v>
       </c>
       <c r="K53" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L53" t="s">
         <v>20</v>
       </c>
       <c r="M53" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>174</v>
@@ -8334,7 +8376,7 @@
         <v>272</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>20</v>
@@ -8375,34 +8417,34 @@
         <v>163</v>
       </c>
       <c r="F54" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="H54" s="21" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="J54" t="s">
         <v>465</v>
       </c>
       <c r="K54" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L54" t="s">
         <v>20</v>
       </c>
       <c r="M54" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>174</v>
       </c>
       <c r="O54" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>221</v>
@@ -8411,7 +8453,7 @@
         <v>272</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>174</v>
@@ -8508,7 +8550,7 @@
     </row>
     <row r="56" spans="1:23">
       <c r="A56" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B56" s="1">
         <f>IFERROR(
@@ -8526,7 +8568,7 @@
         <v>275</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F56" s="22" t="s">
         <v>19</v>
@@ -8535,10 +8577,10 @@
         <v>169</v>
       </c>
       <c r="H56" t="s">
+        <v>636</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>637</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>638</v>
       </c>
       <c r="J56" t="s">
         <v>485</v>
@@ -8893,7 +8935,7 @@
     </row>
     <row r="61" spans="1:23">
       <c r="A61" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B61" s="1">
         <f>IFERROR(
@@ -8908,22 +8950,22 @@
         <v>127</v>
       </c>
       <c r="D61" t="s">
+        <v>676</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" s="22" t="s">
         <v>678</v>
-      </c>
-      <c r="F61" s="22" t="s">
-        <v>679</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>168</v>
       </c>
       <c r="H61" s="22" t="s">
+        <v>679</v>
+      </c>
+      <c r="I61" s="1" t="s">
         <v>680</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>681</v>
       </c>
       <c r="J61" t="s">
         <v>486</v>
@@ -8935,7 +8977,7 @@
         <v>19</v>
       </c>
       <c r="M61" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>19</v>
@@ -8970,7 +9012,7 @@
     </row>
     <row r="62" spans="1:23">
       <c r="A62" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B62" s="1">
         <f>IFERROR(
@@ -8985,7 +9027,7 @@
         <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>242</v>
@@ -8997,13 +9039,13 @@
         <v>168</v>
       </c>
       <c r="H62" t="s">
+        <v>752</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="J62" t="s">
         <v>754</v>
-      </c>
-      <c r="J62" t="s">
-        <v>755</v>
       </c>
       <c r="K62" s="22" t="s">
         <v>233</v>
@@ -9012,7 +9054,7 @@
         <v>470</v>
       </c>
       <c r="M62" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="N62" s="1" t="s">
         <v>20</v>
@@ -9047,7 +9089,7 @@
     </row>
     <row r="63" spans="1:23">
       <c r="A63" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B63" s="1">
         <f>IFERROR(
@@ -9074,16 +9116,16 @@
         <v>168</v>
       </c>
       <c r="H63" t="s">
+        <v>756</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="I63" s="1" t="s">
+      <c r="J63" t="s">
         <v>758</v>
       </c>
-      <c r="J63" t="s">
+      <c r="K63" s="22" t="s">
         <v>759</v>
-      </c>
-      <c r="K63" s="22" t="s">
-        <v>760</v>
       </c>
       <c r="L63" t="s">
         <v>19</v>
@@ -23637,7 +23679,7 @@
     </row>
     <row r="152" spans="1:32">
       <c r="A152" s="24" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B152" s="8">
         <v>759</v>
@@ -23733,7 +23775,7 @@
     </row>
     <row r="153" spans="1:32">
       <c r="A153" s="24" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B153" s="8">
         <v>759</v>
@@ -23829,7 +23871,7 @@
     </row>
     <row r="154" spans="1:32">
       <c r="A154" s="24" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B154" s="8">
         <v>919</v>
@@ -23925,7 +23967,7 @@
     </row>
     <row r="155" spans="1:32">
       <c r="A155" s="24" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B155" s="8">
         <v>6159</v>
@@ -24021,7 +24063,7 @@
     </row>
     <row r="156" spans="1:32">
       <c r="A156" s="24" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B156" s="8">
         <v>4619</v>
@@ -24117,7 +24159,7 @@
     </row>
     <row r="157" spans="1:32">
       <c r="A157" s="24" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B157" s="8">
         <v>6349</v>
@@ -24213,7 +24255,7 @@
     </row>
     <row r="158" spans="1:32">
       <c r="A158" s="24" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B158" s="8">
         <v>6929</v>
@@ -24309,7 +24351,7 @@
     </row>
     <row r="159" spans="1:32">
       <c r="A159" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B159" s="8">
         <v>4699</v>
@@ -24405,7 +24447,7 @@
     </row>
     <row r="160" spans="1:32">
       <c r="A160" s="24" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B160" s="8">
         <v>679</v>
@@ -24501,7 +24543,7 @@
     </row>
     <row r="161" spans="1:32">
       <c r="A161" s="24" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B161" s="8">
         <v>2749</v>
@@ -24597,7 +24639,7 @@
     </row>
     <row r="162" spans="1:32">
       <c r="A162" s="24" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B162" s="8">
         <v>1499</v>
@@ -24693,7 +24735,7 @@
     </row>
     <row r="163" spans="1:32">
       <c r="A163" s="24" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B163" s="8">
         <v>279</v>
@@ -24789,7 +24831,7 @@
     </row>
     <row r="164" spans="1:32">
       <c r="A164" s="24" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B164" s="8">
         <v>729</v>
@@ -24885,7 +24927,7 @@
     </row>
     <row r="165" spans="1:32">
       <c r="A165" s="24" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B165" s="8">
         <v>359</v>
@@ -24981,7 +25023,7 @@
     </row>
     <row r="166" spans="1:32">
       <c r="A166" s="24" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B166" s="8">
         <v>2329</v>
@@ -25077,7 +25119,7 @@
     </row>
     <row r="167" spans="1:32">
       <c r="A167" s="24" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B167" s="8">
         <v>1769</v>
@@ -25173,7 +25215,7 @@
     </row>
     <row r="168" spans="1:32">
       <c r="A168" s="24" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B168" s="8">
         <v>969</v>
@@ -25269,7 +25311,7 @@
     </row>
     <row r="169" spans="1:32">
       <c r="A169" s="24" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B169" s="8">
         <v>889</v>
@@ -25365,7 +25407,7 @@
     </row>
     <row r="170" spans="1:32">
       <c r="A170" s="24" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B170" s="8">
         <v>1449</v>
@@ -25461,7 +25503,7 @@
     </row>
     <row r="171" spans="1:32">
       <c r="A171" s="24" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B171" s="8">
         <v>1869</v>
@@ -25557,7 +25599,7 @@
     </row>
     <row r="172" spans="1:32">
       <c r="A172" s="24" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B172" s="8">
         <v>899</v>
@@ -25653,7 +25695,7 @@
     </row>
     <row r="173" spans="1:32">
       <c r="A173" s="24" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B173" s="8">
         <v>989</v>
@@ -25749,7 +25791,7 @@
     </row>
     <row r="174" spans="1:32">
       <c r="A174" s="24" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B174" s="8">
         <v>1089</v>
@@ -25845,7 +25887,7 @@
     </row>
     <row r="175" spans="1:32">
       <c r="A175" s="24" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B175" s="8">
         <v>4619</v>
@@ -25941,7 +25983,7 @@
     </row>
     <row r="176" spans="1:32">
       <c r="A176" s="24" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B176" s="8">
         <v>5549</v>
@@ -26037,7 +26079,7 @@
     </row>
     <row r="177" spans="1:32">
       <c r="A177" s="24" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B177" s="8">
         <v>6469</v>
@@ -26133,7 +26175,7 @@
     </row>
     <row r="178" spans="1:32">
       <c r="A178" s="24" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B178" s="8">
         <v>999</v>
@@ -26229,7 +26271,7 @@
     </row>
     <row r="179" spans="1:32">
       <c r="A179" s="24" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B179" s="8">
         <v>659</v>
@@ -26325,7 +26367,7 @@
     </row>
     <row r="180" spans="1:32">
       <c r="A180" s="24" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B180" s="8">
         <v>989</v>
@@ -26421,7 +26463,7 @@
     </row>
     <row r="181" spans="1:32">
       <c r="A181" s="24" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B181" s="8">
         <v>1148</v>
@@ -26517,7 +26559,7 @@
     </row>
     <row r="182" spans="1:32">
       <c r="A182" s="24" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B182" s="8">
         <v>3199</v>
@@ -26613,7 +26655,7 @@
     </row>
     <row r="183" spans="1:32">
       <c r="A183" s="24" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B183" s="8">
         <v>3838</v>
@@ -26709,7 +26751,7 @@
     </row>
     <row r="184" spans="1:32">
       <c r="A184" s="23" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B184" s="8">
         <v>1259</v>
@@ -26805,7 +26847,7 @@
     </row>
     <row r="185" spans="1:32">
       <c r="A185" s="23" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B185" s="8">
         <v>1979</v>
@@ -26901,7 +26943,7 @@
     </row>
     <row r="186" spans="1:32">
       <c r="A186" s="23" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B186" s="8">
         <v>2339</v>
@@ -26997,7 +27039,7 @@
     </row>
     <row r="187" spans="1:32">
       <c r="A187" s="23" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B187" s="8">
         <v>849</v>
@@ -27093,7 +27135,7 @@
     </row>
     <row r="188" spans="1:32">
       <c r="A188" s="23" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B188" s="8">
         <v>619</v>
@@ -27189,7 +27231,7 @@
     </row>
     <row r="189" spans="1:32">
       <c r="A189" s="23" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B189" s="8">
         <v>7319</v>
@@ -27285,7 +27327,7 @@
     </row>
     <row r="190" spans="1:32">
       <c r="A190" s="23" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B190" s="25">
         <v>559</v>
@@ -30063,21 +30105,21 @@
         <v>433</v>
       </c>
       <c r="B2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -30085,21 +30127,21 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B5" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -30107,21 +30149,21 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B7" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -30129,10 +30171,10 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -30140,21 +30182,21 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B10" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -30162,10 +30204,10 @@
         <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -30173,10 +30215,10 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -30184,10 +30226,10 @@
         <v>328</v>
       </c>
       <c r="B13" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -30195,21 +30237,21 @@
         <v>379</v>
       </c>
       <c r="B14" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B15" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -30217,21 +30259,21 @@
         <v>422</v>
       </c>
       <c r="B16" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B17" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -30239,21 +30281,21 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B19" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -30261,21 +30303,21 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B21" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -30283,21 +30325,21 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B23" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -30305,10 +30347,10 @@
         <v>419</v>
       </c>
       <c r="B24" t="s">
+        <v>766</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>767</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -30316,10 +30358,10 @@
         <v>425</v>
       </c>
       <c r="B25" t="s">
+        <v>766</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>767</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -30327,32 +30369,32 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B27" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B28" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -30360,10 +30402,10 @@
         <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -30371,21 +30413,21 @@
         <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B31" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -30393,21 +30435,21 @@
         <v>450</v>
       </c>
       <c r="B32" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B33" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -30415,10 +30457,10 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -30426,21 +30468,21 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B36" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -30448,21 +30490,21 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B38" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -30470,10 +30512,10 @@
         <v>525</v>
       </c>
       <c r="B39" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -30481,32 +30523,32 @@
         <v>526</v>
       </c>
       <c r="B40" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B41" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B42" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -30514,10 +30556,10 @@
         <v>530</v>
       </c>
       <c r="B43" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -30525,10 +30567,10 @@
         <v>39</v>
       </c>
       <c r="B44" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -30536,10 +30578,10 @@
         <v>401</v>
       </c>
       <c r="B45" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -30547,43 +30589,43 @@
         <v>524</v>
       </c>
       <c r="B46" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B47" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B48" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B49" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -30591,21 +30633,21 @@
         <v>41</v>
       </c>
       <c r="B50" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B51" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -30613,10 +30655,10 @@
         <v>42</v>
       </c>
       <c r="B52" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -30624,10 +30666,10 @@
         <v>43</v>
       </c>
       <c r="B53" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -30635,10 +30677,10 @@
         <v>44</v>
       </c>
       <c r="B54" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -30646,98 +30688,98 @@
         <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B56" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B57" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B58" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B59" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B60" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B61" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B62" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B63" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
   </sheetData>
@@ -31328,13 +31370,13 @@
         <v>46</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D31" t="s">
         <v>47</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -31345,13 +31387,13 @@
         <v>46</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D32" t="s">
         <v>47</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -31362,13 +31404,13 @@
         <v>46</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D33" t="s">
         <v>47</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -31379,47 +31421,47 @@
         <v>46</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D34" t="s">
         <v>47</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B35" t="s">
         <v>46</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D35" t="s">
         <v>47</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B36" t="s">
         <v>46</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D36" t="s">
         <v>47</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -31430,13 +31472,13 @@
         <v>46</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D37" t="s">
         <v>47</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -31447,353 +31489,353 @@
         <v>46</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D38" t="s">
         <v>47</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D39" t="s">
         <v>47</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D40" t="s">
         <v>47</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B41" t="s">
         <v>46</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D41" t="s">
         <v>47</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B42" t="s">
         <v>46</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D42" t="s">
         <v>47</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B43" t="s">
         <v>46</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D43" t="s">
         <v>47</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B44" t="s">
         <v>46</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D44" t="s">
         <v>47</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B45" t="s">
         <v>46</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D45" t="s">
         <v>47</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B46" t="s">
         <v>46</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D46" t="s">
         <v>47</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B47" t="s">
         <v>46</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D47" t="s">
         <v>47</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B48" t="s">
         <v>46</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D48" t="s">
         <v>47</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B49" t="s">
         <v>46</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D49" t="s">
         <v>47</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B50" t="s">
         <v>46</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D50" t="s">
         <v>47</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B51" t="s">
         <v>46</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D51" t="s">
         <v>47</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B52" t="s">
         <v>46</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D52" t="s">
         <v>47</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B53" t="s">
         <v>46</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D53" t="s">
         <v>47</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B54" t="s">
         <v>46</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D54" t="s">
         <v>47</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B55" t="s">
         <v>46</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D55" t="s">
         <v>47</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B56" t="s">
         <v>46</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D56" t="s">
         <v>47</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B57" t="s">
         <v>46</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D57" t="s">
         <v>47</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B58" t="s">
         <v>46</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D58" t="s">
         <v>47</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
   </sheetData>
